--- a/step by step.xlsx
+++ b/step by step.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB\NJDPB_API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF96E38-2D43-447F-8B7E-5B0582597609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6AB9FC-9C32-4A71-87EC-A61F3A200897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A378D8B9-DBA5-458D-B7BD-E5CCA1952584}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">Create a github branch and base it on an empty branch </t>
   </si>
@@ -139,6 +139,12 @@
   </si>
   <si>
     <t>add security config class</t>
+  </si>
+  <si>
+    <t>add gitignore for .env file</t>
+  </si>
+  <si>
+    <t>configure log</t>
   </si>
 </sst>
 </file>
@@ -510,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC0AA62-8911-408B-BDB1-B430764B13A3}">
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -530,151 +536,161 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>32</v>
       </c>
     </row>

--- a/step by step.xlsx
+++ b/step by step.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB\NJDPB_API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6AB9FC-9C32-4A71-87EC-A61F3A200897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1B83F6-964C-420D-A24C-D7342B9BC4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A378D8B9-DBA5-458D-B7BD-E5CCA1952584}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{A378D8B9-DBA5-458D-B7BD-E5CCA1952584}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t xml:space="preserve">Create a github branch and base it on an empty branch </t>
   </si>
@@ -145,6 +145,45 @@
   </si>
   <si>
     <t>configure log</t>
+  </si>
+  <si>
+    <t>add springdoc</t>
+  </si>
+  <si>
+    <t>add actuator</t>
+  </si>
+  <si>
+    <t>make actuator excape security</t>
+  </si>
+  <si>
+    <t>add validation</t>
+  </si>
+  <si>
+    <t>run the application to verify so far</t>
+  </si>
+  <si>
+    <t>spring initializer</t>
+  </si>
+  <si>
+    <t>SCAFFOLD</t>
+  </si>
+  <si>
+    <t>DEVELOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add all the annotatations for </t>
+  </si>
+  <si>
+    <t>aggregator request</t>
+  </si>
+  <si>
+    <t>controller</t>
+  </si>
+  <si>
+    <t>validation</t>
+  </si>
+  <si>
+    <t>add validation to aggregatRequestdto</t>
   </si>
 </sst>
 </file>
@@ -160,12 +199,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -180,8 +225,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,182 +562,247 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC0AA62-8911-408B-BDB1-B430764B13A3}">
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>8</v>
+      <c r="A18" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>9</v>
+      <c r="A19" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>23</v>
+      <c r="A20" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>24</v>
+      <c r="A21" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>25</v>
+      <c r="A22" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -704,7 +815,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4386186-685F-4607-BFC4-77A57E171651}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/step by step.xlsx
+++ b/step by step.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB\NJDPB_API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1B83F6-964C-420D-A24C-D7342B9BC4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7EA617-85BB-459B-9F37-A1CA99FD142F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{A378D8B9-DBA5-458D-B7BD-E5CCA1952584}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
   <si>
     <t xml:space="preserve">Create a github branch and base it on an empty branch </t>
   </si>
@@ -184,6 +184,18 @@
   </si>
   <si>
     <t>add validation to aggregatRequestdto</t>
+  </si>
+  <si>
+    <t>Create a dummy comtroller to test the service</t>
+  </si>
+  <si>
+    <t>delete the dummy controller</t>
+  </si>
+  <si>
+    <t>Write unit test case for the service</t>
+  </si>
+  <si>
+    <t>create a context path for versioning</t>
   </si>
 </sst>
 </file>
@@ -562,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC0AA62-8911-408B-BDB1-B430764B13A3}">
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -646,163 +658,183 @@
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>23</v>
+      <c r="A28" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>24</v>
+      <c r="A29" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>25</v>
+      <c r="A30" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>45</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/step by step.xlsx
+++ b/step by step.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB\NJDPB_API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7EA617-85BB-459B-9F37-A1CA99FD142F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AF79BB-B3CB-4E4D-8187-A65EFA85F55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{A378D8B9-DBA5-458D-B7BD-E5CCA1952584}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t xml:space="preserve">Create a github branch and base it on an empty branch </t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>create a context path for versioning</t>
+  </si>
+  <si>
+    <t>Repeat the same for processed request</t>
   </si>
 </sst>
 </file>
@@ -574,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC0AA62-8911-408B-BDB1-B430764B13A3}">
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -632,208 +635,213 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I33" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I34" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I35" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I36" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I38" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I39" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I42" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I43" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I44" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I45" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I46" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>51</v>
       </c>
     </row>

--- a/step by step.xlsx
+++ b/step by step.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB\NJDPB_API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AF79BB-B3CB-4E4D-8187-A65EFA85F55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6971F7-2954-4F9A-931A-D18DB6BAA09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{A378D8B9-DBA5-458D-B7BD-E5CCA1952584}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t xml:space="preserve">Create a github branch and base it on an empty branch </t>
   </si>
@@ -120,9 +120,6 @@
     <t>create aggregator controller</t>
   </si>
   <si>
-    <t>add controller advice</t>
-  </si>
-  <si>
     <t>add processed request service in aggregator service</t>
   </si>
   <si>
@@ -199,6 +196,15 @@
   </si>
   <si>
     <t>Repeat the same for processed request</t>
+  </si>
+  <si>
+    <t>add slow db time out exception</t>
+  </si>
+  <si>
+    <t>add argument not valid exception</t>
+  </si>
+  <si>
+    <t>create aggregateresponse dto</t>
   </si>
 </sst>
 </file>
@@ -577,12 +583,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC0AA62-8911-408B-BDB1-B430764B13A3}">
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
@@ -592,7 +598,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
@@ -612,7 +618,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
@@ -622,17 +628,17 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -687,162 +693,175 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="I32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I34" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I35" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I38" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I39" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I40" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I41" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I42" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I43" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I44" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I45" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I46" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>47</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/step by step.xlsx
+++ b/step by step.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB\NJDPB_API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6971F7-2954-4F9A-931A-D18DB6BAA09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5065CCFD-9E6F-4606-814C-8F7205F8FDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{A378D8B9-DBA5-458D-B7BD-E5CCA1952584}"/>
   </bookViews>
@@ -805,12 +805,12 @@
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -825,27 +825,27 @@
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="A69" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="A70" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="A71" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="A72" s="1" t="s">
         <v>44</v>
       </c>
     </row>

--- a/step by step.xlsx
+++ b/step by step.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB\NJDPB_API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5065CCFD-9E6F-4606-814C-8F7205F8FDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB66825A-CEE5-4530-A8B7-7C3195A8C9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{A378D8B9-DBA5-458D-B7BD-E5CCA1952584}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A378D8B9-DBA5-458D-B7BD-E5CCA1952584}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -815,7 +815,7 @@
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="A63" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="A78" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="A81" s="1" t="s">
         <v>53</v>
       </c>
     </row>
